--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N87_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N87_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.9914853030385</v>
+        <v>5.848616361743757</v>
       </c>
       <c r="D2" t="n">
-        <v>36.08874013110391</v>
+        <v>5.864420271304386</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7093855211735</v>
+        <v>0.4402751471906939</v>
       </c>
       <c r="F2" t="n">
-        <v>2.798889576819349</v>
+        <v>0.4548195562331442</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.44748369223398</v>
+        <v>6.897716099988022</v>
       </c>
       <c r="D3" t="n">
-        <v>39.08210745987159</v>
+        <v>6.350842462229133</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7093855211735</v>
+        <v>0.4402751471906939</v>
       </c>
       <c r="F3" t="n">
-        <v>2.798889576819349</v>
+        <v>0.4548195562331442</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.88774572461064</v>
+        <v>6.156758680249229</v>
       </c>
       <c r="D4" t="n">
-        <v>32.24390370184159</v>
+        <v>5.239634351549259</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7093855211735</v>
+        <v>0.4402751471906939</v>
       </c>
       <c r="F4" t="n">
-        <v>2.798889576819349</v>
+        <v>0.4548195562331442</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
